--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1190078258514404</v>
+        <v>0.1292474269866943</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9845298973413629</v>
+        <v>0.9488473655426636</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9917649260714955</v>
+        <v>0.9745479449394199</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998735031202564</v>
+        <v>0.9994518468544443</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1286299228668213</v>
+        <v>0.1281981468200684</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9868977307430697</v>
+        <v>0.9607823558176621</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9917649260714955</v>
+        <v>0.9745479449394199</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998453927025356</v>
+        <v>0.9994518468544443</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1190078258514404</v>
+        <v>0.1292474269866943</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9845298973413629</v>
+        <v>0.9488473655426636</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9917649260714955</v>
+        <v>0.9745479449394199</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998735031202564</v>
+        <v>0.9994518468544443</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1286299228668213</v>
+        <v>0.1281981468200684</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9868977307430697</v>
+        <v>0.9607823558176621</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9917649260714955</v>
+        <v>0.9745479449394199</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998453927025356</v>
+        <v>0.9994518468544443</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1292474269866943</v>
+        <v>7.704506874084473</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9488473655426636</v>
+        <v>0.9078885893354798</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9805194805194806</v>
+        <v>0.9177215189873418</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9745479449394199</v>
+        <v>0.9042719302588844</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9994518468544443</v>
+        <v>0.9919666413299063</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,93 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1281981468200684</v>
+        <v>6.572227478027344</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9607823558176621</v>
+        <v>0.9100525295165802</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9805194805194806</v>
+        <v>0.9177215189873418</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9745479449394199</v>
+        <v>0.9053970684014629</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9994518468544443</v>
+        <v>0.992708122285623</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.689805746078491</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9133368902195146</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9177215189873418</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9053970684014629</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.992708122285623</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.842351198196411</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9129583933927897</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9177215189873418</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9053970684014629</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.992708122285623</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -557,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +692,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1292474269866943</v>
+        <v>7.704506874084473</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9488473655426636</v>
+        <v>0.9078885893354798</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9805194805194806</v>
+        <v>0.9177215189873418</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9745479449394199</v>
+        <v>0.9042719302588844</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9994518468544443</v>
+        <v>0.9919666413299063</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +727,93 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1281981468200684</v>
+        <v>6.572227478027344</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9607823558176621</v>
+        <v>0.9100525295165802</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9805194805194806</v>
+        <v>0.9177215189873418</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9745479449394199</v>
+        <v>0.9053970684014629</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9994518468544443</v>
+        <v>0.992708122285623</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.689805746078491</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9133368902195146</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9177215189873418</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9053970684014629</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.992708122285623</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.842351198196411</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9129583933927897</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9177215189873418</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9053970684014629</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.992708122285623</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.704506874084473</v>
+        <v>4.597485303878784</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9078885893354798</v>
+        <v>0.9076647938003392</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9177215189873418</v>
+        <v>0.9415995397008056</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9042719302588844</v>
+        <v>0.917050276282387</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9919666413299063</v>
+        <v>0.9842451586097263</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6.572227478027344</v>
+        <v>3.698211908340454</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9100525295165802</v>
+        <v>0.9136404067193084</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9177215189873418</v>
+        <v>0.9421749136939011</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9053970684014629</v>
+        <v>0.9186584883836676</v>
       </c>
       <c r="H3" t="n">
-        <v>0.992708122285623</v>
+        <v>0.9811971601994363</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -561,23 +561,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>7.689805746078491</v>
+        <v>4.323774337768555</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9133368902195146</v>
+        <v>0.9143215241723116</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9177215189873418</v>
+        <v>0.9421749136939011</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9053970684014629</v>
+        <v>0.9186584883836676</v>
       </c>
       <c r="H4" t="n">
-        <v>0.992708122285623</v>
+        <v>0.9811971601994363</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -596,23 +596,23 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>7.842351198196411</v>
+        <v>4.59356427192688</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9129583933927897</v>
+        <v>0.9149155890241473</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9177215189873418</v>
+        <v>0.9421749136939011</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9053970684014629</v>
+        <v>0.9186584883836676</v>
       </c>
       <c r="H5" t="n">
-        <v>0.992708122285623</v>
+        <v>0.9811971601994363</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -692,23 +692,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.704506874084473</v>
+        <v>4.597485303878784</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9078885893354798</v>
+        <v>0.9076647938003392</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9177215189873418</v>
+        <v>0.9415995397008056</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9042719302588844</v>
+        <v>0.917050276282387</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9919666413299063</v>
+        <v>0.9842451586097263</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -727,23 +727,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6.572227478027344</v>
+        <v>3.698211908340454</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9100525295165802</v>
+        <v>0.9136404067193084</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9177215189873418</v>
+        <v>0.9421749136939011</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9053970684014629</v>
+        <v>0.9186584883836676</v>
       </c>
       <c r="H3" t="n">
-        <v>0.992708122285623</v>
+        <v>0.9811971601994363</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -762,23 +762,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>7.689805746078491</v>
+        <v>4.323774337768555</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9133368902195146</v>
+        <v>0.9143215241723116</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9177215189873418</v>
+        <v>0.9421749136939011</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9053970684014629</v>
+        <v>0.9186584883836676</v>
       </c>
       <c r="H4" t="n">
-        <v>0.992708122285623</v>
+        <v>0.9811971601994363</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -797,23 +797,23 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>7.842351198196411</v>
+        <v>4.59356427192688</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9129583933927897</v>
+        <v>0.9149155890241473</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9177215189873418</v>
+        <v>0.9421749136939011</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9053970684014629</v>
+        <v>0.9186584883836676</v>
       </c>
       <c r="H5" t="n">
-        <v>0.992708122285623</v>
+        <v>0.9811971601994363</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.597485303878784</v>
+        <v>0.1014575958251953</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9076647938003392</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9415995397008056</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.917050276282387</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9842451586097263</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,93 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.698211908340454</v>
+        <v>0.0909726619720459</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9136404067193084</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9421749136939011</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9186584883836676</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9811971601994363</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.323774337768555</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9143215241723116</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9421749136939011</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9186584883836676</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9811971601994363</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4.59356427192688</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9149155890241473</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9421749136939011</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.9186584883836676</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.9811971601994363</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -627,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.597485303878784</v>
+        <v>0.1014575958251953</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9076647938003392</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9415995397008056</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.917050276282387</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9842451586097263</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -727,93 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.698211908340454</v>
+        <v>0.0909726619720459</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9136404067193084</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9421749136939011</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9186584883836676</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9811971601994363</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.323774337768555</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9143215241723116</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9421749136939011</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9186584883836676</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9811971601994363</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4.59356427192688</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9149155890241473</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9421749136939011</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.9186584883836676</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.9811971601994363</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1014575958251953</v>
+        <v>0.2168271541595459</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.7960401918648962</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8231292517006803</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7430595946243665</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9533354157989726</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0909726619720459</v>
+        <v>0.09805083274841309</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.8047934919754051</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7761899568874639</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9526528298394188</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'uniform'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1368107795715332</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8003056623121468</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8231292517006803</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7585235126585215</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9546022490628905</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1014575958251953</v>
+        <v>0.2168271541595459</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.7960401918648962</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8231292517006803</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7430595946243665</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9533354157989726</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0909726619720459</v>
+        <v>0.09805083274841309</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.8047934919754051</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7761899568874639</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9526528298394188</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'uniform'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1368107795715332</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8003056623121468</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8231292517006803</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7585235126585215</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9546022490628905</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2168271541595459</v>
+        <v>3.018621206283569</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7960401918648962</v>
+        <v>0.8013286401307914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8231292517006803</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7430595946243665</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9533354157989726</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09805083274841309</v>
+        <v>3.456517219543457</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8047934919754051</v>
+        <v>0.81032050938439</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8367346938775511</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7761899568874639</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9526528298394188</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -561,23 +561,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1368107795715332</v>
+        <v>4.075722217559814</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8003056623121468</v>
+        <v>0.8106837161192055</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8231292517006803</v>
+        <v>0.8760069044879172</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7585235126585215</v>
+        <v>0.8238850693483192</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9546022490628905</v>
+        <v>0.918110502926512</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2168271541595459</v>
+        <v>3.018621206283569</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7960401918648962</v>
+        <v>0.8013286401307914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8231292517006803</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7430595946243665</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9533354157989726</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -692,23 +692,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09805083274841309</v>
+        <v>3.456517219543457</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8047934919754051</v>
+        <v>0.81032050938439</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8367346938775511</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7761899568874639</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9526528298394188</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -727,23 +727,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1368107795715332</v>
+        <v>4.075722217559814</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8003056623121468</v>
+        <v>0.8106837161192055</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8231292517006803</v>
+        <v>0.8760069044879172</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7585235126585215</v>
+        <v>0.8238850693483192</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9546022490628905</v>
+        <v>0.918110502926512</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.018621206283569</v>
+        <v>0.2035315036773682</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8013286401307914</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.456517219543457</v>
+        <v>0.111638069152832</v>
       </c>
       <c r="E3" t="n">
-        <v>0.81032050938439</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.075722217559814</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.8106837161192055</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8760069044879172</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.8238850693483192</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.918110502926512</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.018621206283569</v>
+        <v>0.2035315036773682</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8013286401307914</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.456517219543457</v>
+        <v>0.111638069152832</v>
       </c>
       <c r="E3" t="n">
-        <v>0.81032050938439</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.075722217559814</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.8106837161192055</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8760069044879172</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.8238850693483192</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.918110502926512</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2035315036773682</v>
+        <v>0.1505966186523438</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.111638069152832</v>
+        <v>0.1049485206604004</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2035315036773682</v>
+        <v>0.1505966186523438</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.111638069152832</v>
+        <v>0.1049485206604004</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1505966186523438</v>
+        <v>0.1490786075592041</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1049485206604004</v>
+        <v>0.1107301712036133</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1505966186523438</v>
+        <v>0.1490786075592041</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1049485206604004</v>
+        <v>0.1107301712036133</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1490786075592041</v>
+        <v>0.04705023765563965</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -507,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1107301712036133</v>
+        <v>0.07135176658630371</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>
@@ -542,7 +542,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1490786075592041</v>
+        <v>0.04705023765563965</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1107301712036133</v>
+        <v>0.07135176658630371</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04705023765563965</v>
+        <v>3.476128339767456</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.8013286401307914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07135176658630371</v>
+        <v>3.724423885345459</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.81032050938439</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04705023765563965</v>
+        <v>3.476128339767456</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.8013286401307914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07135176658630371</v>
+        <v>3.724423885345459</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.81032050938439</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -488,22 +488,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>3.476128339767456</v>
+        <v>0.2578475475311279</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8013286401307914</v>
+        <v>0.3903844133325238</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.65625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.3299657409432175</v>
       </c>
       <c r="H2" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9343183593749999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>3.724423885345459</v>
+        <v>0.2439596652984619</v>
       </c>
       <c r="E3" t="n">
-        <v>0.81032050938439</v>
+        <v>0.4104620714742294</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.66875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.3392979324706233</v>
       </c>
       <c r="H3" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9153837890624998</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'minkowski'}</t>
         </is>
       </c>
     </row>
@@ -619,22 +619,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>3.476128339767456</v>
+        <v>0.2578475475311279</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8013286401307914</v>
+        <v>0.3903844133325238</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.65625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.3299657409432175</v>
       </c>
       <c r="H2" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9343183593749999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>3.724423885345459</v>
+        <v>0.2439596652984619</v>
       </c>
       <c r="E3" t="n">
-        <v>0.81032050938439</v>
+        <v>0.4104620714742294</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.66875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.3392979324706233</v>
       </c>
       <c r="H3" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9153837890624998</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'minkowski'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2578475475311279</v>
+        <v>4.328197240829468</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3903844133325238</v>
+        <v>0.7816443157726987</v>
       </c>
       <c r="F2" t="n">
-        <v>0.65625</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3299657409432175</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9343183593749999</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2439596652984619</v>
+        <v>3.765619277954102</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4104620714742294</v>
+        <v>0.7887837510961361</v>
       </c>
       <c r="F3" t="n">
-        <v>0.66875</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3392979324706233</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9153837890624998</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'minkowski'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2578475475311279</v>
+        <v>4.328197240829468</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3903844133325238</v>
+        <v>0.7816443157726987</v>
       </c>
       <c r="F2" t="n">
-        <v>0.65625</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3299657409432175</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9343183593749999</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2439596652984619</v>
+        <v>3.765619277954102</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4104620714742294</v>
+        <v>0.7887837510961361</v>
       </c>
       <c r="F3" t="n">
-        <v>0.66875</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3392979324706233</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9153837890624998</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'minkowski'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.328197240829468</v>
+        <v>0.06473898887634277</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7816443157726987</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.765619277954102</v>
+        <v>0.06860542297363281</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7887837510961361</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.328197240829468</v>
+        <v>0.06473898887634277</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7816443157726987</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.765619277954102</v>
+        <v>0.06860542297363281</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7887837510961361</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06473898887634277</v>
+        <v>0.0462803840637207</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06860542297363281</v>
+        <v>0.04892253875732422</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06473898887634277</v>
+        <v>0.0462803840637207</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06860542297363281</v>
+        <v>0.04892253875732422</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0462803840637207</v>
+        <v>0.04709029197692871</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04892253875732422</v>
+        <v>0.07294321060180664</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0462803840637207</v>
+        <v>0.04709029197692871</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04892253875732422</v>
+        <v>0.07294321060180664</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04709029197692871</v>
+        <v>2.142980337142944</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07294321060180664</v>
+        <v>0.1519787311553955</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>
@@ -543,6 +543,41 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1360764503479004</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9918326672831579</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9936655405405406</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04709029197692871</v>
+        <v>2.142980337142944</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -657,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07294321060180664</v>
+        <v>0.1519787311553955</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>
@@ -674,6 +709,41 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1360764503479004</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9918326672831579</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9936655405405406</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.142980337142944</v>
+        <v>0.1147856712341309</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1519787311553955</v>
+        <v>0.08343935012817383</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1360764503479004</v>
+        <v>0.1888899803161621</v>
       </c>
       <c r="E4" t="n">
         <v>0.9918326672831579</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.142980337142944</v>
+        <v>0.1147856712341309</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1519787311553955</v>
+        <v>0.08343935012817383</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1360764503479004</v>
+        <v>0.1888899803161621</v>
       </c>
       <c r="E4" t="n">
         <v>0.9918326672831579</v>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1147856712341309</v>
+        <v>1.94414758682251</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.8013286401307914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08343935012817383</v>
+        <v>2.169837713241577</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.81032050938439</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1888899803161621</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9918326672831579</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9936655405405406</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1147856712341309</v>
+        <v>1.94414758682251</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.8013286401307914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08343935012817383</v>
+        <v>2.169837713241577</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.81032050938439</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1888899803161621</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9918326672831579</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9936655405405406</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.94414758682251</v>
+        <v>21.74544811248779</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8013286401307914</v>
+        <v>0.9825917846771556</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9843450313617749</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.9843447819418814</v>
       </c>
       <c r="H2" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9992675254413582</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.169837713241577</v>
+        <v>26.36697220802307</v>
       </c>
       <c r="E3" t="n">
-        <v>0.81032050938439</v>
+        <v>0.9837584121796732</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9843450313617749</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.9843447819418814</v>
       </c>
       <c r="H3" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9992675254413582</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.94414758682251</v>
+        <v>21.74544811248779</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8013286401307914</v>
+        <v>0.9825917846771556</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9843450313617749</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.9843447819418814</v>
       </c>
       <c r="H2" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9992675254413582</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.169837713241577</v>
+        <v>26.36697220802307</v>
       </c>
       <c r="E3" t="n">
-        <v>0.81032050938439</v>
+        <v>0.9837584121796732</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9843450313617749</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.9843447819418814</v>
       </c>
       <c r="H3" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9992675254413582</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>21.74544811248779</v>
+        <v>23.69982695579529</v>
       </c>
       <c r="E2" t="n">
         <v>0.9825917846771556</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>26.36697220802307</v>
+        <v>23.63667631149292</v>
       </c>
       <c r="E3" t="n">
         <v>0.9837584121796732</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>21.74544811248779</v>
+        <v>23.69982695579529</v>
       </c>
       <c r="E2" t="n">
         <v>0.9825917846771556</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>26.36697220802307</v>
+        <v>23.63667631149292</v>
       </c>
       <c r="E3" t="n">
         <v>0.9837584121796732</v>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>23.69982695579529</v>
+        <v>3.388538360595703</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9825917846771556</v>
+        <v>0.7816443157726987</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9843450313617749</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9843447819418814</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9992675254413582</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>23.63667631149292</v>
+        <v>3.476355314254761</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9837584121796732</v>
+        <v>0.7887837510961361</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9843450313617749</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9843447819418814</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9992675254413582</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>23.69982695579529</v>
+        <v>3.388538360595703</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9825917846771556</v>
+        <v>0.7816443157726987</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9843450313617749</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9843447819418814</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9992675254413582</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>23.63667631149292</v>
+        <v>3.476355314254761</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9837584121796732</v>
+        <v>0.7887837510961361</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9843450313617749</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9843447819418814</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9992675254413582</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.388538360595703</v>
+        <v>7.729877471923828</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7816443157726987</v>
+        <v>0.937197913778761</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9508582177286621</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9419507116201434</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9717784936272238</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.476355314254761</v>
+        <v>8.527689933776855</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7887837510961361</v>
+        <v>0.9413842056504705</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9508582177286621</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9419507116201434</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9717784936272238</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.388538360595703</v>
+        <v>7.729877471923828</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7816443157726987</v>
+        <v>0.937197913778761</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9508582177286621</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9419507116201434</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9717784936272238</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.476355314254761</v>
+        <v>8.527689933776855</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7887837510961361</v>
+        <v>0.9413842056504705</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9508582177286621</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9419507116201434</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9717784936272238</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.729877471923828</v>
+        <v>0.5380501747131348</v>
       </c>
       <c r="E2" t="n">
-        <v>0.937197913778761</v>
+        <v>0.3731252769552402</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9508582177286621</v>
+        <v>0.6775510204081633</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9419507116201434</v>
+        <v>0.4912773562421409</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9717784936272238</v>
+        <v>0.941466576426489</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.527689933776855</v>
+        <v>0.6125397682189941</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9413842056504705</v>
+        <v>0.3930298749540874</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9508582177286621</v>
+        <v>0.6775510204081633</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9419507116201434</v>
+        <v>0.4948636883981792</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9717784936272238</v>
+        <v>0.9371775649035123</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.729877471923828</v>
+        <v>0.5380501747131348</v>
       </c>
       <c r="E2" t="n">
-        <v>0.937197913778761</v>
+        <v>0.3731252769552402</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9508582177286621</v>
+        <v>0.6775510204081633</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9419507116201434</v>
+        <v>0.4912773562421409</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9717784936272238</v>
+        <v>0.941466576426489</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.527689933776855</v>
+        <v>0.6125397682189941</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9413842056504705</v>
+        <v>0.3930298749540874</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9508582177286621</v>
+        <v>0.6775510204081633</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9419507116201434</v>
+        <v>0.4948636883981792</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9717784936272238</v>
+        <v>0.9371775649035123</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5380501747131348</v>
+        <v>0.1143770217895508</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3731252769552402</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6775510204081633</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4912773562421409</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.941466576426489</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6125397682189941</v>
+        <v>0.07122421264648438</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3930298749540874</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6775510204081633</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4948636883981792</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9371775649035123</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1286566257476807</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9918326672831579</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9936655405405406</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5380501747131348</v>
+        <v>0.1143770217895508</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3731252769552402</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6775510204081633</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4912773562421409</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.941466576426489</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6125397682189941</v>
+        <v>0.07122421264648438</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3930298749540874</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6775510204081633</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4948636883981792</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9371775649035123</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1286566257476807</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9918326672831579</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9936655405405406</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1143770217895508</v>
+        <v>0.08651018142700195</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07122421264648438</v>
+        <v>0.108191967010498</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1286566257476807</v>
+        <v>0.1899051666259766</v>
       </c>
       <c r="E4" t="n">
         <v>0.9918326672831579</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1143770217895508</v>
+        <v>0.08651018142700195</v>
       </c>
       <c r="E2" t="n">
         <v>0.9885883726830831</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07122421264648438</v>
+        <v>0.108191967010498</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918380364236208</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1286566257476807</v>
+        <v>0.1899051666259766</v>
       </c>
       <c r="E4" t="n">
         <v>0.9918326672831579</v>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08651018142700195</v>
+        <v>2.732681512832642</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.8396187077676405</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8540540540540541</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8366571952229587</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9265321671105993</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.108191967010498</v>
+        <v>3.780983209609985</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.8401864108199846</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8540540540540541</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8366571952229587</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9265321671105993</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1899051666259766</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9918326672831579</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9936655405405406</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08651018142700195</v>
+        <v>2.732681512832642</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.8396187077676405</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8540540540540541</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8366571952229587</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9265321671105993</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.108191967010498</v>
+        <v>3.780983209609985</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.8401864108199846</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8540540540540541</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8366571952229587</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9265321671105993</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1899051666259766</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9918326672831579</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9936655405405406</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.732681512832642</v>
+        <v>14.4739978313446</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8396187077676405</v>
+        <v>0.9724697886854861</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8540540540540541</v>
+        <v>0.9744846231835079</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8366571952229587</v>
+        <v>0.9744832339482654</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9265321671105993</v>
+        <v>0.9975799262404401</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.780983209609985</v>
+        <v>16.81514263153076</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8401864108199846</v>
+        <v>0.9734836673129882</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8540540540540541</v>
+        <v>0.9740340205024219</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8366571952229587</v>
+        <v>0.9740320919679999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9265321671105993</v>
+        <v>0.9978872640851937</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.732681512832642</v>
+        <v>14.4739978313446</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8396187077676405</v>
+        <v>0.9724697886854861</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8540540540540541</v>
+        <v>0.9744846231835079</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8366571952229587</v>
+        <v>0.9744832339482654</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9265321671105993</v>
+        <v>0.9975799262404401</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -654,22 +654,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.780983209609985</v>
+        <v>16.81514263153076</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8401864108199846</v>
+        <v>0.9734836673129882</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8540540540540541</v>
+        <v>0.9740340205024219</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8366571952229587</v>
+        <v>0.9740320919679999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9265321671105993</v>
+        <v>0.9978872640851937</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>14.4739978313446</v>
+        <v>11.76212882995605</v>
       </c>
       <c r="E2" t="n">
         <v>0.9724697886854861</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>16.81514263153076</v>
+        <v>13.78122329711914</v>
       </c>
       <c r="E3" t="n">
         <v>0.9734836673129882</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>14.4739978313446</v>
+        <v>11.76212882995605</v>
       </c>
       <c r="E2" t="n">
         <v>0.9724697886854861</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>16.81514263153076</v>
+        <v>13.78122329711914</v>
       </c>
       <c r="E3" t="n">
         <v>0.9734836673129882</v>
